--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/^N^N 시설관리유지보수 (독립)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="429" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3F9C2502-1408-4CE9-A046-044DC1DC7BE7}"/>
+  <xr:revisionPtr revIDLastSave="449" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5F2FE66-F7B8-467B-9792-F12FF741EFCD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="248">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2304,10 +2304,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>`39</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve"> 5</t>
     </r>
@@ -2386,6 +2382,81 @@
         <scheme val="minor"/>
       </rPr>
       <t>)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 식당내 의자</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">층 식당내 의자 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+  </si>
+  <si>
+    <t>벤치형의자 판 이탈</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤치형의자 판 이탈 --&gt; 홀가공 작업 진행</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>홀가공 작업 진행(케이블타이로 고정함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">벤치형 의자 보수 수량 총 6대 ---&gt; 지속적인 관찰 필요 함 </t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2683,10 +2754,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -2896,9 +2963,9 @@
     <col min="6" max="6" width="14.42578125" style="20" customWidth="1"/>
     <col min="7" max="7" width="13.140625" style="20" customWidth="1"/>
     <col min="8" max="8" width="28.5703125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="37.5703125" style="20" customWidth="1"/>
+    <col min="9" max="9" width="42" style="20" customWidth="1"/>
     <col min="10" max="10" width="21" style="20" customWidth="1"/>
-    <col min="11" max="11" width="36.7109375" style="20" customWidth="1"/>
+    <col min="11" max="11" width="41.7109375" style="20" customWidth="1"/>
     <col min="12" max="12" width="14.7109375" style="21" customWidth="1"/>
     <col min="13" max="13" width="15.28515625" style="20" customWidth="1"/>
     <col min="14" max="14" width="10.28515625" style="20" customWidth="1"/>
@@ -4831,12 +4898,12 @@
         <v>235</v>
       </c>
       <c r="P41" s="30" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
-        <v>236</v>
+      <c r="A42" s="2">
+        <v>39</v>
       </c>
       <c r="B42" s="7">
         <v>46244</v>
@@ -4881,29 +4948,63 @@
         <v>235</v>
       </c>
       <c r="P42" s="30" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="4"/>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="4"/>
-      <c r="E43" s="4"/>
-      <c r="F43" s="4"/>
-      <c r="G43" s="4"/>
-      <c r="H43" s="4"/>
-      <c r="I43" s="4"/>
-      <c r="J43" s="4"/>
-      <c r="K43" s="4"/>
-      <c r="L43" s="6"/>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
-      <c r="P43" s="1"/>
+      <c r="A43" s="4">
+        <v>40</v>
+      </c>
+      <c r="B43" s="7">
+        <v>46244</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="G43" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="L43" s="6">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O43" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P43" s="27" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="44" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="4"/>
+      <c r="A44" s="4">
+        <v>41</v>
+      </c>
       <c r="B44" s="7"/>
       <c r="C44" s="7"/>
       <c r="D44" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/^N^N 시설관리유지보수 (독립)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="449" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C5F2FE66-F7B8-467B-9792-F12FF741EFCD}"/>
+  <xr:revisionPtr revIDLastSave="467" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51B848FD-597E-4B6C-9A84-22ADC5E38444}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="257">
   <si>
     <t xml:space="preserve">일자 </t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2422,10 +2422,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>TO20</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>부분보수</t>
   </si>
   <si>
@@ -2457,6 +2453,98 @@
         <charset val="129"/>
       </rPr>
       <t xml:space="preserve">벤치형 의자 보수 수량 총 6대 ---&gt; 지속적인 관찰 필요 함 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 여자휴게실</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선풍기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-21</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">작동 안됨 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이탈 및 먼지 쌓임 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 분해 청소 및 부품 재조립</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회전축 이상으로 고정형으로만  사용 가능 함</t>
     </r>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2754,6 +2842,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -4139,7 +4231,7 @@
         <v>18000</v>
       </c>
       <c r="M26" s="3" t="s">
-        <v>87</v>
+        <v>22</v>
       </c>
       <c r="N26" s="3" t="s">
         <v>23</v>
@@ -4968,22 +5060,22 @@
         <v>240</v>
       </c>
       <c r="F43" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G43" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="G43" s="25" t="s">
+      <c r="H43" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="H43" s="3" t="s">
+      <c r="I43" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="I43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="J43" s="3" t="s">
+      <c r="K43" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="L43" s="6">
         <v>0</v>
@@ -4998,28 +5090,58 @@
         <v>24</v>
       </c>
       <c r="P43" s="27" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
-      <c r="B44" s="7"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="6"/>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
-      <c r="P44" s="1"/>
+      <c r="B44" s="7">
+        <v>46244</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="L44" s="6">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O44" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="P44" s="27" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="45" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="467" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51B848FD-597E-4B6C-9A84-22ADC5E38444}"/>
+  <xr:revisionPtr revIDLastSave="522" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{741B5F8D-5536-4FA6-8CBB-04B3FA65F560}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="sa" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$P$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,11 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="257">
-  <si>
-    <t xml:space="preserve">일자 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="275">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -1872,38 +1868,6 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>무상</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> A/S (6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>번 실외기)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">GHP </t>
     </r>
     <r>
@@ -2184,10 +2148,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>무상 A/S(3번 실외기)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">GHP </t>
     </r>
@@ -2209,10 +2169,6 @@
   </si>
   <si>
     <t>압축기 선</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>무상 A/S(1번 실외기)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -2300,7 +2256,301 @@
     </r>
   </si>
   <si>
-    <t>예정</t>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 식당내 의자</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">층 식당내 의자 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+  </si>
+  <si>
+    <t>벤치형의자 판 이탈</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>벤치형의자 판 이탈 --&gt; 홀가공 작업 진행</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>홀가공 작업 진행(케이블타이로 고정함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">벤치형 의자 보수 수량 총 6대 ---&gt; 지속적인 관찰 필요 함 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 여자휴게실</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>선풍기</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-20</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-21</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분보수</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">작동 안됨 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>부품</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">이탈 및 먼지 쌓임 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 분해 청소 및 부품 재조립</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>회전축 이상으로 고정형으로만  사용 가능 함</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">층 1호 접착기 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">형광등 </t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-22</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>부픔교체</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">전등 계속 깜박임 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">안정기 불량 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>아쎄이 전부 교체(2층 창고쪽과 맞교체 함)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> LED </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">형광등의 내구연수는 7년 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t>~10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 (현 제품 단종) --&gt; 기존 정상제품(2층 창고문앞쪽)과 맞교체 진행 함</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>설비</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>층 시야기</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>반자동 핸드자키</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO24</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>상.하 작동 레버 파손</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>외부 충격에 의한 작동 레버 파손</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">프라스틱으로 규격에 맞게 가공 장착함 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>임시조치 한 상태임,  추후 가공제품 소손시  부품 교체 예정 임</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -2325,7 +2575,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(20,882</t>
+      <t>(10,715</t>
     </r>
     <r>
       <rPr>
@@ -2335,23 +2585,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>시간(2회째))</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> 5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
+      <t>시간(1회쨰)</t>
     </r>
     <r>
       <rPr>
@@ -2361,7 +2595,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>(10,406</t>
+      <t>)_#4</t>
     </r>
     <r>
       <rPr>
@@ -2371,7 +2605,7 @@
         <family val="2"/>
         <charset val="129"/>
       </rPr>
-      <t>시간(1회쨰)</t>
+      <t>번</t>
     </r>
     <r>
       <rPr>
@@ -2381,171 +2615,178 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>층 식당내 의자</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">층 식당내 의자 </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>부분보수</t>
-  </si>
-  <si>
-    <t>벤치형의자 판 이탈</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>벤치형의자 판 이탈 --&gt; 홀가공 작업 진행</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>부분보수</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>홀가공 작업 진행(케이블타이로 고정함)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">벤치형 의자 보수 수량 총 6대 ---&gt; 지속적인 관찰 필요 함 </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>층 여자휴게실</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>선풍기</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO-20</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO-21</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>부분보수</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">작동 안됨 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>부품</t>
+      <t>(260827)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">이탈 및 먼지 쌓임 </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체 분해 청소 및 부품 재조립</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>회전축 이상으로 고정형으로만  사용 가능 함</t>
-    </r>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(21,327</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>시간(2회째))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_#5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(260827)</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(1번 실외기)/  #1번: 12,979(26.8.27기준)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve"> 5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>년 무상 협약에 따른 소모품 50% 할인율 적용</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  (#2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번: 13,587(26.8.27기준))</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>무상 A/S(3번 실외기)  (#3번: 15,051(26.8.27기준))</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>무상</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve"> A/S (6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번 실외기)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">  (#6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>번: 12,345(26.8.27기준))</t>
+    </r>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">접수일자 </t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>수리완료일자</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -2728,7 +2969,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2821,9 +3062,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3045,2145 +3283,2261 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P999"/>
+  <dimension ref="A1:Q999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="20" customWidth="1"/>
-    <col min="2" max="3" width="12.85546875" style="18" customWidth="1"/>
-    <col min="4" max="4" width="33" style="20" customWidth="1"/>
-    <col min="5" max="5" width="31.140625" style="20" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="20" customWidth="1"/>
-    <col min="7" max="7" width="13.140625" style="20" customWidth="1"/>
-    <col min="8" max="8" width="28.5703125" style="20" customWidth="1"/>
-    <col min="9" max="9" width="42" style="20" customWidth="1"/>
-    <col min="10" max="10" width="21" style="20" customWidth="1"/>
-    <col min="11" max="11" width="41.7109375" style="20" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="21" customWidth="1"/>
-    <col min="13" max="13" width="15.28515625" style="20" customWidth="1"/>
-    <col min="14" max="14" width="10.28515625" style="20" customWidth="1"/>
-    <col min="15" max="15" width="14.28515625" style="20" customWidth="1"/>
-    <col min="16" max="16" width="73.85546875" customWidth="1"/>
-    <col min="17" max="29" width="6.5703125" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" style="18" customWidth="1"/>
+    <col min="3" max="3" width="16.7109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="18" customWidth="1"/>
+    <col min="5" max="5" width="33" style="20" customWidth="1"/>
+    <col min="6" max="6" width="31.140625" style="20" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="20" customWidth="1"/>
+    <col min="9" max="9" width="28.5703125" style="20" customWidth="1"/>
+    <col min="10" max="10" width="42" style="20" customWidth="1"/>
+    <col min="11" max="11" width="21" style="20" customWidth="1"/>
+    <col min="12" max="12" width="44.28515625" style="20" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="21" customWidth="1"/>
+    <col min="14" max="14" width="15.28515625" style="20" customWidth="1"/>
+    <col min="15" max="15" width="10.28515625" style="20" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="20" customWidth="1"/>
+    <col min="17" max="17" width="87.85546875" customWidth="1"/>
+    <col min="18" max="30" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D1" s="19"/>
+        <v>30</v>
+      </c>
+      <c r="E1" s="19"/>
     </row>
-    <row r="2" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:16" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="F3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="11" t="s">
+      <c r="G3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="H3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="I3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="J3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="K3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="L3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="M3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="12" t="s">
+      <c r="N3" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="M3" s="11" t="s">
+      <c r="O3" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="N3" s="11" t="s">
+      <c r="P3" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q3" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="O3" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="P3" s="11" t="s">
-        <v>11</v>
-      </c>
     </row>
-    <row r="4" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
       <c r="B4" s="7">
         <v>46056</v>
       </c>
-      <c r="C4" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="H4" s="2" t="s">
+      <c r="C4" s="7"/>
+      <c r="D4" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="L4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K4" s="5" t="s">
+      <c r="M4" s="6">
+        <v>7500</v>
+      </c>
+      <c r="N4" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L4" s="6">
-        <v>7500</v>
-      </c>
-      <c r="M4" s="3" t="s">
+      <c r="O4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N4" s="3" t="s">
+      <c r="P4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O4" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" s="4"/>
+      <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
       <c r="B5" s="7">
         <v>46064</v>
       </c>
-      <c r="C5" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="7"/>
+      <c r="D5" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H5" s="2" t="s">
+      <c r="J5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="6">
+        <v>0</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="L5" s="6">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>30</v>
-      </c>
     </row>
-    <row r="6" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
       <c r="B6" s="7">
         <v>46058</v>
       </c>
-      <c r="C6" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="C6" s="7"/>
+      <c r="D6" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H6" s="2" t="s">
+      <c r="H6" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="2" t="s">
+      <c r="M6" s="6">
+        <v>8000</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="L6" s="6">
-        <v>8000</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N6" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P6" s="4"/>
+      <c r="P6" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
       <c r="B7" s="7">
         <v>46063</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="7"/>
+      <c r="D7" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="H7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="K7" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="L7" s="6">
+      <c r="M7" s="6">
         <v>4750</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="N7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N7" s="3" t="s">
+      <c r="P7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O7" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
       <c r="B8" s="7">
         <v>46073</v>
       </c>
-      <c r="C8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="7"/>
+      <c r="D8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="G8" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="I8" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="L8" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="L8" s="6">
+      <c r="M8" s="6">
         <v>14500</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="N8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="3" t="s">
+      <c r="P8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O8" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P8" s="4"/>
+      <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
       <c r="B9" s="7">
         <v>46091</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="7"/>
+      <c r="D9" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="G9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="H9" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="I9" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="K9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="L9" s="6">
+      <c r="M9" s="6">
         <v>26500</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N9" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O9" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="4"/>
+      <c r="N9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
       <c r="B10" s="7">
         <v>46093</v>
       </c>
-      <c r="C10" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>32</v>
+      <c r="C10" s="7"/>
+      <c r="D10" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="H10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H10" s="3" t="s">
+      <c r="J10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="I10" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="K10" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="L10" s="6">
+        <v>19</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="M10" s="6">
         <v>9000</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P10" s="4"/>
+      <c r="N10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
       <c r="B11" s="7">
         <v>46114</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="7"/>
+      <c r="D11" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="I11" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="K11" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="L11" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="M11" s="6">
+        <v>3500</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q11" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="L11" s="6">
-        <v>3500</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N11" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O11" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P11" s="16" t="s">
-        <v>80</v>
-      </c>
     </row>
-    <row r="12" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
       <c r="B12" s="7">
         <v>46118</v>
       </c>
-      <c r="C12" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>82</v>
+      <c r="C12" s="7"/>
+      <c r="D12" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="2" t="s">
+      <c r="F12" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="G12" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="K12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="3" t="s">
+      <c r="M12" s="6">
+        <v>750000</v>
+      </c>
+      <c r="N12" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L12" s="6">
-        <v>750000</v>
-      </c>
-      <c r="M12" s="3" t="s">
+      <c r="O12" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N12" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O12" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P12" s="1"/>
+      <c r="P12" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
       <c r="B13" s="7">
         <v>46113</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="C13" s="7"/>
+      <c r="D13" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="H13" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="3" t="s">
+      <c r="J13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="J13" s="3" t="s">
+      <c r="L13" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="K13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="L13" s="6">
+      <c r="M13" s="6">
         <v>15000</v>
       </c>
-      <c r="M13" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="N13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O13" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P13" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
       <c r="B14" s="7">
         <v>46114</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C14" s="7"/>
+      <c r="D14" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="G14" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>62</v>
-      </c>
       <c r="H14" s="3" t="s">
-        <v>100</v>
+        <v>61</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>99</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="L14" s="6">
+        <v>98</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="M14" s="6">
         <v>50</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N14" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O14" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P14" s="15" t="s">
-        <v>101</v>
+      <c r="N14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O14" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q14" s="15" t="s">
+        <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
       <c r="B15" s="7">
         <v>46118</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="C15" s="7"/>
+      <c r="D15" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="G15" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="H15" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="I15" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="H15" s="3" t="s">
+      <c r="J15" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="K15" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="K15" s="3" t="s">
+      <c r="M15" s="6">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O15" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="P15" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q15" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="L15" s="6">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N15" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="O15" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="P15" s="15" t="s">
-        <v>109</v>
-      </c>
     </row>
-    <row r="16" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
       <c r="B16" s="7">
         <v>46115</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="C16" s="7"/>
+      <c r="D16" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E16" s="3" t="s">
+      <c r="G16" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="H16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="I16" s="3" t="s">
+      <c r="K16" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="L16" s="6">
+      <c r="M16" s="6">
         <v>0</v>
       </c>
-      <c r="M16" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="N16" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O16" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P16" s="1"/>
+        <v>21</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
       <c r="B17" s="7">
         <v>46107</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="C17" s="7"/>
+      <c r="D17" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H17" s="3" t="s">
+      <c r="J17" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I17" s="3" t="s">
+      <c r="K17" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L17" s="6">
+      <c r="M17" s="6">
         <v>30000</v>
       </c>
-      <c r="M17" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="N17" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P17" s="15"/>
+        <v>21</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P17" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q17" s="15"/>
     </row>
-    <row r="18" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
       <c r="B18" s="7">
         <v>46206</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="3" t="s">
+      <c r="C18" s="7"/>
+      <c r="D18" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="J18" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="L18" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="M18" s="6">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L18" s="6">
-        <v>0</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N18" s="3" t="s">
+      <c r="P18" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q18" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="O18" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P18" s="15" t="s">
-        <v>128</v>
-      </c>
     </row>
-    <row r="19" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
       <c r="B19" s="7">
         <v>46219</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" s="7"/>
+      <c r="D19" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F19" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D19" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="G19" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>135</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>134</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="J19" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="L19" s="6">
+      <c r="M19" s="6">
         <v>200000</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="N19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O19" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N19" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O19" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P19" s="1"/>
+      <c r="P19" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
       <c r="B20" s="7">
         <v>46219</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D20" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="C20" s="7"/>
+      <c r="D20" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F20" s="2" t="s">
+      <c r="H20" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="I20" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="J20" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="L20" s="6">
+        <v>136</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M20" s="6">
         <v>400000</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="N20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O20" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N20" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O20" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P20" s="1"/>
+      <c r="P20" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:16" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
       <c r="B21" s="7">
         <v>46219</v>
       </c>
-      <c r="C21" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="D21" s="3" t="s">
+      <c r="C21" s="7"/>
+      <c r="D21" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H21" s="3" t="s">
+      <c r="J21" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="I21" s="3" t="s">
+      <c r="K21" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="L21" s="6">
+      <c r="M21" s="6">
         <v>0</v>
       </c>
-      <c r="M21" s="3" t="s">
-        <v>22</v>
-      </c>
       <c r="N21" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O21" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P21" s="16" t="s">
-        <v>142</v>
+        <v>21</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q21" s="16" t="s">
+        <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
       <c r="B22" s="7">
         <v>46227</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="7"/>
+      <c r="D22" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="H22" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="H22" s="3" t="s">
+      <c r="J22" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I22" s="3" t="s">
+      <c r="K22" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="L22" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="L22" s="6">
+      <c r="M22" s="6">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="N22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O22" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N22" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O22" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P22" s="1"/>
+      <c r="P22" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
       <c r="B23" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="24"/>
+      <c r="D23" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="F23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="G23" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="H23" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="I23" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="H23" s="3" t="s">
+      <c r="J23" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="I23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="J23" s="3" t="s">
+      <c r="L23" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="M23" s="6">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O23" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="L23" s="6">
-        <v>0</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="O23" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P23" s="1"/>
+      <c r="P23" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
       <c r="B24" s="7">
         <v>46228</v>
       </c>
-      <c r="C24" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>152</v>
+      <c r="C24" s="7"/>
+      <c r="D24" s="13" t="s">
+        <v>144</v>
       </c>
       <c r="E24" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G24" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F24" s="2" t="s">
+      <c r="H24" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="G24" s="25" t="s">
+      <c r="I24" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H24" s="3" t="s">
+      <c r="J24" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I24" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L24" s="6">
+      <c r="M24" s="6">
         <v>2100000</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="N24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O24" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="O24" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P24" s="1"/>
+      <c r="P24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:16" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
       <c r="B25" s="7">
         <v>46233</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" s="7"/>
+      <c r="D25" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="F25" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="G25" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="H25" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I25" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="G25" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H25" s="26" t="s">
+      <c r="J25" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="I25" s="3" t="s">
+      <c r="K25" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="3" t="s">
+      <c r="M25" s="6">
+        <v>150000</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O25" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L25" s="6">
-        <v>150000</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N25" s="3" t="s">
+      <c r="P25" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q25" s="27" t="s">
         <v>173</v>
       </c>
-      <c r="O25" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P25" s="27" t="s">
-        <v>174</v>
-      </c>
     </row>
-    <row r="26" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
       <c r="B26" s="7">
         <v>46244</v>
       </c>
-      <c r="C26" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D26" s="3" t="s">
+      <c r="C26" s="7"/>
+      <c r="D26" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="G26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="H26" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="G26" s="3" t="s">
+      <c r="I26" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H26" s="3" t="s">
+      <c r="J26" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="I26" s="3" t="s">
+      <c r="K26" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L26" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="J26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K26" s="5" t="s">
+      <c r="M26" s="6">
+        <v>18000</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q26" s="27" t="s">
         <v>180</v>
       </c>
-      <c r="L26" s="6">
-        <v>18000</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O26" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P26" s="27" t="s">
-        <v>181</v>
-      </c>
     </row>
-    <row r="27" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
       <c r="B27" s="7">
         <v>44552</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" s="7"/>
+      <c r="D27" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="G27" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="H27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I27" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="G27" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H27" s="3" t="s">
+      <c r="J27" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I27" s="3" t="s">
+      <c r="K27" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="3" t="s">
+      <c r="M27" s="6">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q27" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="L27" s="6">
-        <v>0</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N27" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O27" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P27" s="15" t="s">
-        <v>189</v>
-      </c>
     </row>
-    <row r="28" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
       <c r="B28" s="7">
         <v>44553</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="C28" s="7"/>
+      <c r="D28" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I28" s="3" t="s">
+      <c r="K28" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="J28" s="3" t="s">
+      <c r="L28" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="K28" s="3" t="s">
+      <c r="M28" s="6">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q28" s="28" t="s">
         <v>193</v>
       </c>
-      <c r="L28" s="6">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O28" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P28" s="28" t="s">
-        <v>194</v>
-      </c>
     </row>
-    <row r="29" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
       <c r="B29" s="7">
         <v>44566</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="C29" s="7"/>
+      <c r="D29" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I29" s="3" t="s">
+      <c r="K29" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="L29" s="6">
+      <c r="M29" s="6">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N29" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O29" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P29" s="28" t="s">
-        <v>194</v>
+      <c r="Q29" s="28" t="s">
+        <v>193</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
       <c r="B30" s="7">
         <v>44650</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D30" s="3" t="s">
+      <c r="C30" s="7"/>
+      <c r="D30" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="G30" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="H30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I30" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="G30" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H30" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="I30" s="3" t="s">
+      <c r="J30" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="L30" s="6">
+      <c r="M30" s="6">
         <v>0</v>
       </c>
-      <c r="M30" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N30" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P30" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O30" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P30" s="28" t="s">
-        <v>202</v>
+      <c r="Q30" s="28" t="s">
+        <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
       <c r="B31" s="7">
         <v>44830</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="C31" s="7"/>
+      <c r="D31" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="J31" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="K31" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I31" s="3" t="s">
+      <c r="M31" s="6">
+        <v>1000000</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P31" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q31" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="J31" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="L31" s="6">
-        <v>1000000</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N31" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O31" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P31" s="29" t="s">
-        <v>208</v>
-      </c>
     </row>
-    <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
       <c r="B32" s="7">
         <v>44903</v>
       </c>
-      <c r="C32" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E32" s="2" t="s">
+      <c r="C32" s="7">
+        <v>46261</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L32" s="5" t="s">
         <v>209</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="M32" s="6">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P32" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q32" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="5" t="s">
-        <v>211</v>
-      </c>
-      <c r="L32" s="6">
-        <v>0</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O32" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P32" s="15" t="s">
-        <v>212</v>
-      </c>
     </row>
-    <row r="33" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
       <c r="B33" s="7">
         <v>44931</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E33" s="2" t="s">
+      <c r="C33" s="7">
+        <v>46261</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="M33" s="6">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P33" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q33" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L33" s="6">
-        <v>0</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N33" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O33" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P33" s="15" t="s">
-        <v>215</v>
-      </c>
     </row>
-    <row r="34" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
       <c r="B34" s="7">
         <v>44930</v>
       </c>
-      <c r="C34" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>203</v>
+      <c r="C34" s="7"/>
+      <c r="D34" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>41</v>
+        <v>201</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>186</v>
+        <v>40</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="K34" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="M34" s="6">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P34" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q34" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="L34" s="6">
-        <v>0</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="N34" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O34" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P34" s="15" t="s">
-        <v>219</v>
-      </c>
     </row>
-    <row r="35" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
       <c r="B35" s="7">
         <v>44935</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>203</v>
+      <c r="C35" s="7"/>
+      <c r="D35" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>41</v>
+        <v>201</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="H35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J35" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="5" t="s">
-        <v>220</v>
-      </c>
-      <c r="L35" s="6">
+      <c r="K35" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L35" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="M35" s="6">
         <v>0</v>
       </c>
-      <c r="M35" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P35" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O35" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P35" s="15" t="s">
-        <v>218</v>
+      <c r="Q35" s="15" t="s">
+        <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
       <c r="B36" s="7">
         <v>44937</v>
       </c>
-      <c r="C36" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>209</v>
+      <c r="C36" s="7"/>
+      <c r="D36" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>41</v>
+        <v>207</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="H36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J36" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I36" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="K36" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="L36" s="6">
+        <v>19</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="M36" s="6">
         <v>0</v>
       </c>
-      <c r="M36" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P36" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O36" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P36" s="15" t="s">
-        <v>221</v>
+      <c r="Q36" s="15" t="s">
+        <v>219</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
       <c r="B37" s="7">
         <v>44938</v>
       </c>
-      <c r="C37" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D37" s="5" t="s">
+      <c r="C37" s="7"/>
+      <c r="D37" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E37" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="H37" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L37" s="6">
+      <c r="M37" s="6">
         <v>0</v>
       </c>
-      <c r="M37" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P37" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O37" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P37" s="15" t="s">
-        <v>226</v>
+      <c r="Q37" s="15" t="s">
+        <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
       <c r="B38" s="7">
         <v>44938</v>
       </c>
-      <c r="C38" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>227</v>
+      <c r="C38" s="7"/>
+      <c r="D38" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>41</v>
+        <v>224</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>225</v>
       </c>
       <c r="H38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J38" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I38" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="K38" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="L38" s="6">
+        <v>19</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="M38" s="6">
         <v>0</v>
       </c>
-      <c r="M38" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P38" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O38" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P38" s="15" t="s">
-        <v>230</v>
+      <c r="Q38" s="15" t="s">
+        <v>269</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
       <c r="B39" s="7">
         <v>45740</v>
       </c>
-      <c r="C39" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>231</v>
+      <c r="C39" s="7"/>
+      <c r="D39" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>206</v>
+        <v>227</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="L39" s="6">
+        <v>176</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="M39" s="6">
         <v>400000</v>
       </c>
-      <c r="M39" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P39" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O39" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P39" s="30" t="s">
-        <v>233</v>
+      <c r="Q39" s="30" t="s">
+        <v>270</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
       <c r="B40" s="7">
         <v>45827</v>
       </c>
-      <c r="C40" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>234</v>
+      <c r="C40" s="7"/>
+      <c r="D40" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>206</v>
+        <v>230</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>228</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="K40" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="L40" s="6">
+        <v>176</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="M40" s="6">
         <v>400000</v>
       </c>
-      <c r="M40" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P40" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P40" s="30" t="s">
-        <v>233</v>
+      <c r="Q40" s="30" t="s">
+        <v>229</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
       <c r="B41" s="7">
         <v>46244</v>
       </c>
-      <c r="C41" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E41" s="2" t="s">
+      <c r="C41" s="7"/>
+      <c r="D41" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="J41" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="G41" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H41" s="2" t="s">
+      <c r="K41" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="L41" s="6">
+      <c r="M41" s="6">
         <v>400000</v>
       </c>
-      <c r="M41" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P41" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O41" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="P41" s="30" t="s">
-        <v>236</v>
+      <c r="Q41" s="30" t="s">
+        <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>39</v>
       </c>
       <c r="B42" s="7">
         <v>46244</v>
       </c>
-      <c r="C42" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>209</v>
+      <c r="C42" s="7"/>
+      <c r="D42" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>197</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="H42" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I42" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="L42" s="6">
+      <c r="M42" s="6">
         <v>400000</v>
       </c>
-      <c r="M42" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="N42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P42" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O42" s="31" t="s">
-        <v>235</v>
-      </c>
-      <c r="P42" s="30" t="s">
-        <v>237</v>
+      <c r="Q42" s="30" t="s">
+        <v>267</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
       <c r="B43" s="7">
         <v>46244</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="7"/>
+      <c r="D43" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="H43" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="M43" s="6">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P43" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q43" s="27" t="s">
         <v>239</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G43" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="L43" s="6">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="O43" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P43" s="27" t="s">
-        <v>246</v>
-      </c>
     </row>
-    <row r="44" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
       <c r="B44" s="7">
         <v>46244</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="7"/>
+      <c r="D44" s="13" t="s">
+        <v>240</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J44" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="K44" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="E44" s="3" t="s">
+      <c r="M44" s="6">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P44" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q44" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="F44" s="2" t="s">
+    </row>
+    <row r="45" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="4">
+        <v>42</v>
+      </c>
+      <c r="B45" s="7">
+        <v>46246</v>
+      </c>
+      <c r="C45" s="7"/>
+      <c r="D45" s="13" t="s">
+        <v>250</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G44" s="3" t="s">
+      <c r="F45" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="H44" s="3" t="s">
+      <c r="G45" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="I44" s="5" t="s">
+      <c r="H45" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="J44" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="K44" s="3" t="s">
+      <c r="I45" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="L44" s="6">
+      <c r="J45" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="K45" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="M45" s="6">
         <v>0</v>
       </c>
-      <c r="M44" s="3" t="s">
+      <c r="N45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O45" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="N44" s="3" t="s">
+      <c r="P45" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="O44" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="P44" s="27" t="s">
-        <v>256</v>
+      <c r="Q45" s="27" t="s">
+        <v>258</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="4"/>
-      <c r="B45" s="7"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="4"/>
-      <c r="E45" s="4"/>
-      <c r="F45" s="4"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="4"/>
-      <c r="I45" s="4"/>
-      <c r="J45" s="4"/>
-      <c r="K45" s="4"/>
-      <c r="L45" s="6"/>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
-      <c r="P45" s="1"/>
+    <row r="46" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="4">
+        <v>43</v>
+      </c>
+      <c r="B46" s="7">
+        <v>46260</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="D46" s="13" t="s">
+        <v>259</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="M46" s="6">
+        <v>0</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="P46" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q46" s="15" t="s">
+        <v>266</v>
+      </c>
     </row>
-    <row r="46" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="4"/>
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4"/>
-      <c r="L46" s="6"/>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
-      <c r="P46" s="1"/>
-    </row>
-    <row r="47" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="4"/>
       <c r="B47" s="7"/>
       <c r="C47" s="7"/>
-      <c r="D47" s="4"/>
+      <c r="D47" s="7"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
       <c r="G47" s="4"/>
@@ -5191,17 +5545,18 @@
       <c r="I47" s="4"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
-      <c r="L47" s="6"/>
-      <c r="M47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="6"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="1"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="1"/>
     </row>
-    <row r="48" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
-      <c r="D48" s="4"/>
+      <c r="D48" s="7"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
       <c r="G48" s="4"/>
@@ -5209,17 +5564,18 @@
       <c r="I48" s="4"/>
       <c r="J48" s="4"/>
       <c r="K48" s="4"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="6"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="1"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
-      <c r="D49" s="4"/>
+      <c r="D49" s="7"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
       <c r="G49" s="4"/>
@@ -5227,17 +5583,18 @@
       <c r="I49" s="4"/>
       <c r="J49" s="4"/>
       <c r="K49" s="4"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="6"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="1"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
-      <c r="D50" s="4"/>
+      <c r="D50" s="7"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
       <c r="G50" s="4"/>
@@ -5245,17 +5602,18 @@
       <c r="I50" s="4"/>
       <c r="J50" s="4"/>
       <c r="K50" s="4"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="6"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="1"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
-      <c r="D51" s="4"/>
+      <c r="D51" s="7"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
       <c r="G51" s="4"/>
@@ -5263,17 +5621,18 @@
       <c r="I51" s="4"/>
       <c r="J51" s="4"/>
       <c r="K51" s="4"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="6"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
-      <c r="P51" s="1"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
-      <c r="D52" s="4"/>
+      <c r="D52" s="7"/>
       <c r="E52" s="4"/>
       <c r="F52" s="4"/>
       <c r="G52" s="4"/>
@@ -5281,17 +5640,18 @@
       <c r="I52" s="4"/>
       <c r="J52" s="4"/>
       <c r="K52" s="4"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="6"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="1"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
-      <c r="D53" s="4"/>
+      <c r="D53" s="7"/>
       <c r="E53" s="4"/>
       <c r="F53" s="4"/>
       <c r="G53" s="4"/>
@@ -5299,17 +5659,18 @@
       <c r="I53" s="4"/>
       <c r="J53" s="4"/>
       <c r="K53" s="4"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="4"/>
+      <c r="L53" s="4"/>
+      <c r="M53" s="6"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="1"/>
+      <c r="P53" s="4"/>
+      <c r="Q53" s="1"/>
     </row>
-    <row r="54" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
-      <c r="D54" s="4"/>
+      <c r="D54" s="7"/>
       <c r="E54" s="4"/>
       <c r="F54" s="4"/>
       <c r="G54" s="4"/>
@@ -5317,17 +5678,18 @@
       <c r="I54" s="4"/>
       <c r="J54" s="4"/>
       <c r="K54" s="4"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="4"/>
+      <c r="L54" s="4"/>
+      <c r="M54" s="6"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="1"/>
+      <c r="P54" s="4"/>
+      <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
-      <c r="D55" s="4"/>
+      <c r="D55" s="7"/>
       <c r="E55" s="4"/>
       <c r="F55" s="4"/>
       <c r="G55" s="4"/>
@@ -5335,17 +5697,18 @@
       <c r="I55" s="4"/>
       <c r="J55" s="4"/>
       <c r="K55" s="4"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="4"/>
+      <c r="L55" s="4"/>
+      <c r="M55" s="6"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
-      <c r="P55" s="1"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="1"/>
     </row>
-    <row r="56" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
-      <c r="D56" s="4"/>
+      <c r="D56" s="7"/>
       <c r="E56" s="4"/>
       <c r="F56" s="4"/>
       <c r="G56" s="4"/>
@@ -5353,20 +5716,21 @@
       <c r="I56" s="4"/>
       <c r="J56" s="4"/>
       <c r="K56" s="4"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="4"/>
+      <c r="L56" s="4"/>
+      <c r="M56" s="6"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="1"/>
+      <c r="P56" s="4"/>
+      <c r="Q56" s="1"/>
     </row>
-    <row r="57" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -6303,7 +6667,7 @@
     <row r="998" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A3:P13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A3:Q13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/^N^N 시설관리유지보수 (독립)/facility/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="566" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFEA1D08-6FDC-4AB3-A096-587B0FC6378A}"/>
+  <xr:revisionPtr revIDLastSave="567" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{053A7CE7-C1D3-4419-83B8-9F256E84F078}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2534,10 +2534,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>TO24</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>상.하 작동 레버 파손</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2791,6 +2787,10 @@
   </si>
   <si>
     <t>25/628</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>TO-24</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3084,6 +3084,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -3318,10 +3322,10 @@
         <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C3" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>41</v>
@@ -4764,7 +4768,7 @@
         <v>23</v>
       </c>
       <c r="Q30" s="28" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5135,7 +5139,7 @@
         <v>23</v>
       </c>
       <c r="Q37" s="15" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="38" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5188,7 +5192,7 @@
         <v>23</v>
       </c>
       <c r="Q38" s="15" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="39" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5241,7 +5245,7 @@
         <v>23</v>
       </c>
       <c r="Q39" s="30" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="40" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5252,7 +5256,7 @@
         <v>45827</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>182</v>
@@ -5347,7 +5351,7 @@
         <v>23</v>
       </c>
       <c r="Q41" s="30" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="42" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5400,7 +5404,7 @@
         <v>23</v>
       </c>
       <c r="Q42" s="30" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="43" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -5582,22 +5586,22 @@
         <v>261</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I46" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J46" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M46" s="6">
         <v>0</v>
@@ -5612,7 +5616,7 @@
         <v>109</v>
       </c>
       <c r="Q46" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="47" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/삼화당피앤티_통합대시보드_멀티파일.OLD/HP-IN-MH4/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a0b077ce2e0caad7/바탕 화면/^N^N 시설관리유지보수 (독립)/facility/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="607" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{834610BA-EA03-4A38-9FE8-A2424AD70DE8}"/>
+  <xr:revisionPtr revIDLastSave="566" documentId="13_ncr:1_{AC06454F-31E3-4034-8C74-D409704AECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFEA1D08-6FDC-4AB3-A096-587B0FC6378A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="sa" sheetId="3" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$V$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">sa!$A$3:$Q$13</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="276">
   <si>
     <t>대상설비명</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -2534,6 +2534,10 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
+    <t>TO24</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
     <t>상.하 작동 레버 파손</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -2787,100 +2791,6 @@
   </si>
   <si>
     <t>25/628</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>특정이슈 발생일</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>특정이슈 발생이력</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>특정이슈 발생 종료일</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>특정 이슈 내용</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>특정이슈 증빙자료</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>설비</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>층 화물리프트</t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>화물리프트</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>월간유지보수</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>이상 없음</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>전체 정기 점검 진행</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-      </rPr>
-      <t>완료</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Aptos Narrow"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">승강기 유지보수료 인상의 건(월10,000원 인상) - 자재비 등 물가 상승으로 인한 월 유지 보수료 인상 요인 발생 </t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO-24</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>TO-26</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>임시조치(프라스틱 자체가공 부착)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -3063,7 +2973,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -3157,24 +3067,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -3190,10 +3082,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3395,7 +3283,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:V999"/>
+  <dimension ref="A1:Q999"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" style="20" customWidth="1"/>
@@ -3405,7 +3293,7 @@
     <col min="5" max="5" width="33" style="20" customWidth="1"/>
     <col min="6" max="6" width="31.140625" style="20" customWidth="1"/>
     <col min="7" max="7" width="14.42578125" style="20" customWidth="1"/>
-    <col min="8" max="8" width="16.5703125" style="20" customWidth="1"/>
+    <col min="8" max="8" width="13.140625" style="20" customWidth="1"/>
     <col min="9" max="9" width="28.5703125" style="20" customWidth="1"/>
     <col min="10" max="10" width="42" style="20" customWidth="1"/>
     <col min="11" max="11" width="21" style="20" customWidth="1"/>
@@ -3414,30 +3302,26 @@
     <col min="14" max="14" width="15.28515625" style="20" customWidth="1"/>
     <col min="15" max="15" width="10.28515625" style="20" customWidth="1"/>
     <col min="16" max="16" width="14.28515625" style="20" customWidth="1"/>
-    <col min="17" max="18" width="30.28515625" style="20" customWidth="1"/>
-    <col min="19" max="19" width="30.28515625" style="33" customWidth="1"/>
-    <col min="20" max="20" width="30.28515625" style="20" customWidth="1"/>
-    <col min="21" max="21" width="30.28515625" style="33" customWidth="1"/>
-    <col min="22" max="22" width="87.85546875" customWidth="1"/>
-    <col min="23" max="35" width="6.5703125" customWidth="1"/>
+    <col min="17" max="17" width="87.85546875" customWidth="1"/>
+    <col min="18" max="30" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>30</v>
       </c>
       <c r="E1" s="19"/>
     </row>
-    <row r="2" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="3" spans="1:22" ht="39" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="3" spans="1:17" ht="39" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D3" s="10" t="s">
         <v>41</v>
@@ -3479,25 +3363,10 @@
         <v>14</v>
       </c>
       <c r="Q3" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="R3" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="S3" s="34" t="s">
-        <v>275</v>
-      </c>
-      <c r="T3" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="U3" s="34" t="s">
-        <v>277</v>
-      </c>
-      <c r="V3" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -3546,14 +3415,9 @@
       <c r="P4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="8"/>
-      <c r="R4" s="8"/>
-      <c r="S4" s="35"/>
-      <c r="T4" s="8"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="4"/>
+      <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>2</v>
       </c>
@@ -3602,16 +3466,11 @@
       <c r="P5" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="8"/>
-      <c r="R5" s="8"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="8"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
         <v>3</v>
       </c>
@@ -3660,14 +3519,9 @@
       <c r="P6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" s="8"/>
-      <c r="R6" s="8"/>
-      <c r="S6" s="35"/>
-      <c r="T6" s="8"/>
-      <c r="U6" s="35"/>
-      <c r="V6" s="4"/>
+      <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
         <v>4</v>
       </c>
@@ -3716,14 +3570,9 @@
       <c r="P7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q7" s="8"/>
-      <c r="R7" s="8"/>
-      <c r="S7" s="35"/>
-      <c r="T7" s="8"/>
-      <c r="U7" s="35"/>
-      <c r="V7" s="4"/>
+      <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
         <v>5</v>
       </c>
@@ -3772,14 +3621,9 @@
       <c r="P8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="8"/>
-      <c r="R8" s="8"/>
-      <c r="S8" s="35"/>
-      <c r="T8" s="8"/>
-      <c r="U8" s="35"/>
-      <c r="V8" s="4"/>
+      <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="4">
         <v>6</v>
       </c>
@@ -3828,14 +3672,9 @@
       <c r="P9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="8"/>
-      <c r="S9" s="35"/>
-      <c r="T9" s="8"/>
-      <c r="U9" s="35"/>
-      <c r="V9" s="4"/>
+      <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4">
         <v>7</v>
       </c>
@@ -3884,14 +3723,9 @@
       <c r="P10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="8"/>
-      <c r="R10" s="8"/>
-      <c r="S10" s="35"/>
-      <c r="T10" s="8"/>
-      <c r="U10" s="35"/>
-      <c r="V10" s="4"/>
+      <c r="Q10" s="4"/>
     </row>
-    <row r="11" spans="1:22" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>8</v>
       </c>
@@ -3940,16 +3774,11 @@
       <c r="P11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q11" s="8"/>
-      <c r="R11" s="8"/>
-      <c r="S11" s="35"/>
-      <c r="T11" s="8"/>
-      <c r="U11" s="35"/>
-      <c r="V11" s="16" t="s">
+      <c r="Q11" s="16" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="4">
         <v>9</v>
       </c>
@@ -3998,14 +3827,9 @@
       <c r="P12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="8"/>
-      <c r="S12" s="35"/>
-      <c r="T12" s="8"/>
-      <c r="U12" s="35"/>
-      <c r="V12" s="1"/>
+      <c r="Q12" s="1"/>
     </row>
-    <row r="13" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>10</v>
       </c>
@@ -4054,14 +3878,9 @@
       <c r="P13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q13" s="8"/>
-      <c r="R13" s="8"/>
-      <c r="S13" s="35"/>
-      <c r="T13" s="8"/>
-      <c r="U13" s="35"/>
-      <c r="V13" s="1"/>
+      <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>11</v>
       </c>
@@ -4110,16 +3929,11 @@
       <c r="P14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q14" s="8"/>
-      <c r="R14" s="8"/>
-      <c r="S14" s="35"/>
-      <c r="T14" s="8"/>
-      <c r="U14" s="35"/>
-      <c r="V14" s="15" t="s">
+      <c r="Q14" s="15" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>12</v>
       </c>
@@ -4168,16 +3982,11 @@
       <c r="P15" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="36"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="36"/>
-      <c r="V15" s="15" t="s">
+      <c r="Q15" s="15" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="16" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>13</v>
       </c>
@@ -4226,14 +4035,9 @@
       <c r="P16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q16" s="8"/>
-      <c r="R16" s="8"/>
-      <c r="S16" s="35"/>
-      <c r="T16" s="8"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="1"/>
+      <c r="Q16" s="1"/>
     </row>
-    <row r="17" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>14</v>
       </c>
@@ -4282,14 +4086,9 @@
       <c r="P17" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q17" s="8"/>
-      <c r="R17" s="8"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="8"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="15"/>
+      <c r="Q17" s="15"/>
     </row>
-    <row r="18" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="4">
         <v>15</v>
       </c>
@@ -4338,16 +4137,11 @@
       <c r="P18" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="35"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="15" t="s">
+      <c r="Q18" s="15" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="4">
         <v>16</v>
       </c>
@@ -4396,14 +4190,9 @@
       <c r="P19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q19" s="8"/>
-      <c r="R19" s="8"/>
-      <c r="S19" s="35"/>
-      <c r="T19" s="8"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="1"/>
+      <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4">
         <v>17</v>
       </c>
@@ -4452,14 +4241,9 @@
       <c r="P20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q20" s="8"/>
-      <c r="R20" s="8"/>
-      <c r="S20" s="35"/>
-      <c r="T20" s="8"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="1"/>
+      <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:22" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="4">
         <v>18</v>
       </c>
@@ -4508,16 +4292,11 @@
       <c r="P21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q21" s="8"/>
-      <c r="R21" s="8"/>
-      <c r="S21" s="35"/>
-      <c r="T21" s="8"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="16" t="s">
+      <c r="Q21" s="16" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4">
         <v>19</v>
       </c>
@@ -4566,14 +4345,9 @@
       <c r="P22" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q22" s="8"/>
-      <c r="R22" s="8"/>
-      <c r="S22" s="35"/>
-      <c r="T22" s="8"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="1"/>
+      <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>20</v>
       </c>
@@ -4622,14 +4396,9 @@
       <c r="P23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q23" s="8"/>
-      <c r="R23" s="8"/>
-      <c r="S23" s="35"/>
-      <c r="T23" s="8"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="1"/>
+      <c r="Q23" s="1"/>
     </row>
-    <row r="24" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="4">
         <v>21</v>
       </c>
@@ -4678,14 +4447,9 @@
       <c r="P24" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
-      <c r="S24" s="35"/>
-      <c r="T24" s="8"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="1"/>
+      <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:22" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4">
         <v>22</v>
       </c>
@@ -4734,16 +4498,11 @@
       <c r="P25" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q25" s="8"/>
-      <c r="R25" s="8"/>
-      <c r="S25" s="35"/>
-      <c r="T25" s="8"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="27" t="s">
+      <c r="Q25" s="27" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="4">
         <v>23</v>
       </c>
@@ -4792,16 +4551,11 @@
       <c r="P26" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="35"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="27" t="s">
+      <c r="Q26" s="27" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>24</v>
       </c>
@@ -4850,16 +4604,11 @@
       <c r="P27" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q27" s="8"/>
-      <c r="R27" s="8"/>
-      <c r="S27" s="35"/>
-      <c r="T27" s="8"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="15" t="s">
+      <c r="Q27" s="15" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="4">
         <v>25</v>
       </c>
@@ -4908,16 +4657,11 @@
       <c r="P28" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q28" s="8"/>
-      <c r="R28" s="8"/>
-      <c r="S28" s="35"/>
-      <c r="T28" s="8"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="28" t="s">
+      <c r="Q28" s="28" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="29" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>26</v>
       </c>
@@ -4966,16 +4710,11 @@
       <c r="P29" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q29" s="8"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="35"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="28" t="s">
+      <c r="Q29" s="28" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="30" spans="1:22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4">
         <v>27</v>
       </c>
@@ -5024,16 +4763,11 @@
       <c r="P30" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q30" s="8"/>
-      <c r="R30" s="8"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="8"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="28" t="s">
-        <v>271</v>
+      <c r="Q30" s="28" t="s">
+        <v>272</v>
       </c>
     </row>
-    <row r="31" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>28</v>
       </c>
@@ -5082,16 +4816,11 @@
       <c r="P31" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q31" s="8"/>
-      <c r="R31" s="8"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="8"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="29" t="s">
+      <c r="Q31" s="29" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="32" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="4">
         <v>29</v>
       </c>
@@ -5140,16 +4869,11 @@
       <c r="P32" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q32" s="8"/>
-      <c r="R32" s="8"/>
-      <c r="S32" s="35"/>
-      <c r="T32" s="8"/>
-      <c r="U32" s="35"/>
-      <c r="V32" s="15" t="s">
+      <c r="Q32" s="15" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>30</v>
       </c>
@@ -5198,16 +4922,11 @@
       <c r="P33" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q33" s="8"/>
-      <c r="R33" s="8"/>
-      <c r="S33" s="35"/>
-      <c r="T33" s="8"/>
-      <c r="U33" s="35"/>
-      <c r="V33" s="15" t="s">
+      <c r="Q33" s="15" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="4">
         <v>31</v>
       </c>
@@ -5256,16 +4975,11 @@
       <c r="P34" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q34" s="8"/>
-      <c r="R34" s="8"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="8"/>
-      <c r="U34" s="35"/>
-      <c r="V34" s="15" t="s">
+      <c r="Q34" s="15" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>32</v>
       </c>
@@ -5314,16 +5028,11 @@
       <c r="P35" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q35" s="8"/>
-      <c r="R35" s="8"/>
-      <c r="S35" s="35"/>
-      <c r="T35" s="8"/>
-      <c r="U35" s="35"/>
-      <c r="V35" s="15" t="s">
+      <c r="Q35" s="15" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="4">
         <v>33</v>
       </c>
@@ -5372,16 +5081,11 @@
       <c r="P36" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
-      <c r="S36" s="35"/>
-      <c r="T36" s="8"/>
-      <c r="U36" s="35"/>
-      <c r="V36" s="15" t="s">
+      <c r="Q36" s="15" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="37" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4">
         <v>34</v>
       </c>
@@ -5430,16 +5134,11 @@
       <c r="P37" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q37" s="8"/>
-      <c r="R37" s="8"/>
-      <c r="S37" s="35"/>
-      <c r="T37" s="8"/>
-      <c r="U37" s="35"/>
-      <c r="V37" s="15" t="s">
-        <v>270</v>
+      <c r="Q37" s="15" t="s">
+        <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="4">
         <v>35</v>
       </c>
@@ -5488,16 +5187,11 @@
       <c r="P38" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q38" s="8"/>
-      <c r="R38" s="8"/>
-      <c r="S38" s="35"/>
-      <c r="T38" s="8"/>
-      <c r="U38" s="35"/>
-      <c r="V38" s="15" t="s">
-        <v>268</v>
+      <c r="Q38" s="15" t="s">
+        <v>269</v>
       </c>
     </row>
-    <row r="39" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>36</v>
       </c>
@@ -5546,16 +5240,11 @@
       <c r="P39" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q39" s="8"/>
-      <c r="R39" s="8"/>
-      <c r="S39" s="35"/>
-      <c r="T39" s="8"/>
-      <c r="U39" s="35"/>
-      <c r="V39" s="30" t="s">
-        <v>269</v>
+      <c r="Q39" s="30" t="s">
+        <v>270</v>
       </c>
     </row>
-    <row r="40" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="4">
         <v>37</v>
       </c>
@@ -5563,7 +5252,7 @@
         <v>45827</v>
       </c>
       <c r="C40" s="24" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D40" s="13" t="s">
         <v>182</v>
@@ -5604,16 +5293,11 @@
       <c r="P40" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q40" s="8"/>
-      <c r="R40" s="8"/>
-      <c r="S40" s="35"/>
-      <c r="T40" s="8"/>
-      <c r="U40" s="35"/>
-      <c r="V40" s="30" t="s">
+      <c r="Q40" s="30" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="41" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="4">
         <v>38</v>
       </c>
@@ -5662,16 +5346,11 @@
       <c r="P41" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q41" s="8"/>
-      <c r="R41" s="8"/>
-      <c r="S41" s="35"/>
-      <c r="T41" s="8"/>
-      <c r="U41" s="35"/>
-      <c r="V41" s="30" t="s">
-        <v>267</v>
+      <c r="Q41" s="30" t="s">
+        <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>39</v>
       </c>
@@ -5720,16 +5399,11 @@
       <c r="P42" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q42" s="8"/>
-      <c r="R42" s="8"/>
-      <c r="S42" s="35"/>
-      <c r="T42" s="8"/>
-      <c r="U42" s="35"/>
-      <c r="V42" s="30" t="s">
-        <v>266</v>
+      <c r="Q42" s="30" t="s">
+        <v>267</v>
       </c>
     </row>
-    <row r="43" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="4">
         <v>40</v>
       </c>
@@ -5778,16 +5452,11 @@
       <c r="P43" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q43" s="8"/>
-      <c r="R43" s="8"/>
-      <c r="S43" s="35"/>
-      <c r="T43" s="8"/>
-      <c r="U43" s="35"/>
-      <c r="V43" s="27" t="s">
+      <c r="Q43" s="27" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="44" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="4">
         <v>41</v>
       </c>
@@ -5836,16 +5505,11 @@
       <c r="P44" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q44" s="8"/>
-      <c r="R44" s="8"/>
-      <c r="S44" s="35"/>
-      <c r="T44" s="8"/>
-      <c r="U44" s="35"/>
-      <c r="V44" s="27" t="s">
+      <c r="Q44" s="27" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="45" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>42</v>
       </c>
@@ -5894,16 +5558,11 @@
       <c r="P45" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="Q45" s="8"/>
-      <c r="R45" s="8"/>
-      <c r="S45" s="35"/>
-      <c r="T45" s="8"/>
-      <c r="U45" s="35"/>
-      <c r="V45" s="27" t="s">
+      <c r="Q45" s="27" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="4">
         <v>43</v>
       </c>
@@ -5923,22 +5582,22 @@
         <v>261</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J46" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M46" s="6">
         <v>0</v>
@@ -5952,80 +5611,30 @@
       <c r="P46" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="Q46" s="22" t="s">
-        <v>290</v>
-      </c>
-      <c r="R46" s="22"/>
-      <c r="S46" s="36">
-        <v>46260</v>
-      </c>
-      <c r="T46" s="22"/>
-      <c r="U46" s="36"/>
-      <c r="V46" s="15" t="s">
-        <v>265</v>
+      <c r="Q46" s="15" t="s">
+        <v>266</v>
       </c>
     </row>
-    <row r="47" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
-        <v>44</v>
-      </c>
-      <c r="B47" s="7">
-        <v>46260</v>
-      </c>
-      <c r="C47" s="7">
-        <v>46260</v>
-      </c>
-      <c r="D47" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="M47" s="6">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="O47" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="P47" s="31" t="s">
-        <v>286</v>
-      </c>
-      <c r="Q47" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="R47" s="4"/>
-      <c r="S47" s="32">
-        <v>46260</v>
-      </c>
-      <c r="T47" s="4"/>
-      <c r="U47" s="32"/>
-      <c r="V47" s="1"/>
+    <row r="47" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="B47" s="7"/>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="4"/>
+      <c r="I47" s="4"/>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4"/>
+      <c r="L47" s="4"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
+      <c r="P47" s="4"/>
+      <c r="Q47" s="1"/>
     </row>
-    <row r="48" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="4"/>
       <c r="B48" s="7"/>
       <c r="C48" s="7"/>
@@ -6042,14 +5651,9 @@
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
       <c r="P48" s="4"/>
-      <c r="Q48" s="4"/>
-      <c r="R48" s="4"/>
-      <c r="S48" s="32"/>
-      <c r="T48" s="4"/>
-      <c r="U48" s="32"/>
-      <c r="V48" s="1"/>
+      <c r="Q48" s="1"/>
     </row>
-    <row r="49" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="4"/>
       <c r="B49" s="7"/>
       <c r="C49" s="7"/>
@@ -6066,14 +5670,9 @@
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
       <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="32"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="32"/>
-      <c r="V49" s="1"/>
+      <c r="Q49" s="1"/>
     </row>
-    <row r="50" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="4"/>
       <c r="B50" s="7"/>
       <c r="C50" s="7"/>
@@ -6090,14 +5689,9 @@
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
       <c r="P50" s="4"/>
-      <c r="Q50" s="4"/>
-      <c r="R50" s="4"/>
-      <c r="S50" s="32"/>
-      <c r="T50" s="4"/>
-      <c r="U50" s="32"/>
-      <c r="V50" s="1"/>
+      <c r="Q50" s="1"/>
     </row>
-    <row r="51" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="4"/>
       <c r="B51" s="7"/>
       <c r="C51" s="7"/>
@@ -6114,14 +5708,9 @@
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
       <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="32"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="32"/>
-      <c r="V51" s="1"/>
+      <c r="Q51" s="1"/>
     </row>
-    <row r="52" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="4"/>
       <c r="B52" s="7"/>
       <c r="C52" s="7"/>
@@ -6138,14 +5727,9 @@
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
       <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4"/>
-      <c r="S52" s="32"/>
-      <c r="T52" s="4"/>
-      <c r="U52" s="32"/>
-      <c r="V52" s="1"/>
+      <c r="Q52" s="1"/>
     </row>
-    <row r="53" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="4"/>
       <c r="B53" s="7"/>
       <c r="C53" s="7"/>
@@ -6162,14 +5746,9 @@
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
       <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="32"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="32"/>
-      <c r="V53" s="1"/>
+      <c r="Q53" s="1"/>
     </row>
-    <row r="54" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="4"/>
       <c r="B54" s="7"/>
       <c r="C54" s="7"/>
@@ -6186,14 +5765,9 @@
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
       <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="32"/>
-      <c r="T54" s="4"/>
-      <c r="U54" s="32"/>
-      <c r="V54" s="1"/>
+      <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="4"/>
       <c r="B55" s="7"/>
       <c r="C55" s="7"/>
@@ -6210,14 +5784,9 @@
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
       <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="32"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="32"/>
-      <c r="V55" s="1"/>
+      <c r="Q55" s="1"/>
     </row>
-    <row r="56" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="4"/>
       <c r="B56" s="7"/>
       <c r="C56" s="7"/>
@@ -6234,21 +5803,16 @@
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
       <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="32"/>
-      <c r="T56" s="4"/>
-      <c r="U56" s="32"/>
-      <c r="V56" s="1"/>
+      <c r="Q56" s="1"/>
     </row>
-    <row r="57" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="58" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="59" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="60" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="61" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="62" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="63" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="64" spans="1:22" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="66" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -7185,7 +6749,7 @@
     <row r="998" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="999" ht="16.5" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A3:V13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A3:Q13" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
